--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J443"/>
+  <dimension ref="A1:J445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16390,6 +16390,78 @@
         <v>351.17</v>
       </c>
       <c r="J443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>324.36</v>
+      </c>
+      <c r="C444" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="D444" t="n">
+        <v>326.53</v>
+      </c>
+      <c r="E444" t="n">
+        <v>331</v>
+      </c>
+      <c r="F444" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="G444" t="n">
+        <v>334.86</v>
+      </c>
+      <c r="H444" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="I444" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>324.17</v>
+      </c>
+      <c r="C445" t="n">
+        <v>324.07</v>
+      </c>
+      <c r="D445" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="E445" t="n">
+        <v>330.72</v>
+      </c>
+      <c r="F445" t="n">
+        <v>334.82</v>
+      </c>
+      <c r="G445" t="n">
+        <v>334</v>
+      </c>
+      <c r="H445" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="I445" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="J445" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16406,7 +16478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21069,6 +21141,26 @@
       </c>
       <c r="B466" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -21237,28 +21329,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2992646366082286</v>
+        <v>-0.3056748809444349</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1253517106326697</v>
+        <v>0.130334366339046</v>
       </c>
       <c r="M2" t="n">
-        <v>4.838313145771789</v>
+        <v>4.85118111338569</v>
       </c>
       <c r="N2" t="n">
-        <v>37.57143278641804</v>
+        <v>37.66654199887364</v>
       </c>
       <c r="O2" t="n">
-        <v>6.129554044660838</v>
+        <v>6.137307389961305</v>
       </c>
       <c r="P2" t="n">
-        <v>340.0628194122859</v>
+        <v>340.1297426795393</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21315,28 +21407,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3622224518901088</v>
+        <v>-0.3663394211977466</v>
       </c>
       <c r="J3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1994408765212791</v>
+        <v>0.2040290242235062</v>
       </c>
       <c r="M3" t="n">
-        <v>4.570383300703447</v>
+        <v>4.571321963455968</v>
       </c>
       <c r="N3" t="n">
-        <v>31.66458055752791</v>
+        <v>31.63118581754031</v>
       </c>
       <c r="O3" t="n">
-        <v>5.627128979997519</v>
+        <v>5.624160898973313</v>
       </c>
       <c r="P3" t="n">
-        <v>338.6053686541836</v>
+        <v>338.6483476907003</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21393,28 +21485,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2363437875446329</v>
+        <v>-0.2388080055570191</v>
       </c>
       <c r="J4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.159379176342599</v>
+        <v>0.163150015885964</v>
       </c>
       <c r="M4" t="n">
-        <v>3.371632747296073</v>
+        <v>3.367444506351017</v>
       </c>
       <c r="N4" t="n">
-        <v>17.71335059368641</v>
+        <v>17.67262813185996</v>
       </c>
       <c r="O4" t="n">
-        <v>4.208723154792485</v>
+        <v>4.203882506904772</v>
       </c>
       <c r="P4" t="n">
-        <v>335.901595038543</v>
+        <v>335.9273210212963</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21471,28 +21563,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04835885891767457</v>
+        <v>-0.05091203855506196</v>
       </c>
       <c r="J5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01390801924975682</v>
+        <v>0.01547001683335369</v>
       </c>
       <c r="M5" t="n">
-        <v>2.482286698337871</v>
+        <v>2.484562460312208</v>
       </c>
       <c r="N5" t="n">
-        <v>9.968917539028594</v>
+        <v>9.966026059585223</v>
       </c>
       <c r="O5" t="n">
-        <v>3.157359266701937</v>
+        <v>3.156901338272266</v>
       </c>
       <c r="P5" t="n">
-        <v>335.2409216335918</v>
+        <v>335.2675778806471</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21549,28 +21641,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02051946940904694</v>
+        <v>0.01813493454810108</v>
       </c>
       <c r="J6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002045655810144709</v>
+        <v>0.001608736212026729</v>
       </c>
       <c r="M6" t="n">
-        <v>2.852011615958245</v>
+        <v>2.849863523021642</v>
       </c>
       <c r="N6" t="n">
-        <v>12.34963531436038</v>
+        <v>12.33078721873343</v>
       </c>
       <c r="O6" t="n">
-        <v>3.514204791181126</v>
+        <v>3.511522065818957</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3513751875424</v>
+        <v>337.3762714933046</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21627,28 +21719,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1032471356408707</v>
+        <v>-0.1057743405776874</v>
       </c>
       <c r="J7" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K7" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03244270690256168</v>
+        <v>0.0342312853234833</v>
       </c>
       <c r="M7" t="n">
-        <v>3.655242243483534</v>
+        <v>3.650851851176482</v>
       </c>
       <c r="N7" t="n">
-        <v>19.1143441986771</v>
+        <v>19.07012165070148</v>
       </c>
       <c r="O7" t="n">
-        <v>4.371995448153748</v>
+        <v>4.36693504081541</v>
       </c>
       <c r="P7" t="n">
-        <v>340.2593800954958</v>
+        <v>340.2857676988257</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21705,28 +21797,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2060110640720947</v>
+        <v>-0.2078344771059488</v>
       </c>
       <c r="J8" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K8" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1121209352943822</v>
+        <v>0.1147255762690159</v>
       </c>
       <c r="M8" t="n">
-        <v>3.712042398236513</v>
+        <v>3.705215100122515</v>
       </c>
       <c r="N8" t="n">
-        <v>20.2065404716719</v>
+        <v>20.1370449708586</v>
       </c>
       <c r="O8" t="n">
-        <v>4.495168569883881</v>
+        <v>4.487431890386594</v>
       </c>
       <c r="P8" t="n">
-        <v>345.8808715108977</v>
+        <v>345.8999093931506</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21783,28 +21875,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1265389626691696</v>
+        <v>-0.1277792468717529</v>
       </c>
       <c r="J9" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K9" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1176677008777737</v>
+        <v>0.1205499154309083</v>
       </c>
       <c r="M9" t="n">
-        <v>2.106641558643504</v>
+        <v>2.104615050888059</v>
       </c>
       <c r="N9" t="n">
-        <v>7.218836740406545</v>
+        <v>7.196276095445568</v>
       </c>
       <c r="O9" t="n">
-        <v>2.686789299592833</v>
+        <v>2.682587574608808</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6582413094969</v>
+        <v>356.6711908435022</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21842,7 +21934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J443"/>
+  <dimension ref="A1:J445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44881,6 +44973,110 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-42.52598140636716,173.5024919905367</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-42.526639317497576,173.5023913229718</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-42.52730037714111,173.50233366723305</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-42.527963737833176,173.5022953844388</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-42.528630301370754,173.5022647858875</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-42.529295256209146,173.50223289971788</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-42.52996093219644,173.50224790393113</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-42.530618617038904,173.5024554558913</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-42.525981237485304,173.5024896885341</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-42.52663967304087,173.50239616934363</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-42.52730042158414,173.5023342730359</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-42.52796350391668,173.50229198996115</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-42.52863008298952,173.50225955864005</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-42.5292950554535,173.50222243196652</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-42.52996097454227,173.5022433991659</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-42.530618728020556,173.50245253746988</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J445"/>
+  <dimension ref="A1:J446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16464,6 +16464,42 @@
       <c r="J445" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>325.81</v>
+      </c>
+      <c r="C446" t="n">
+        <v>325.51</v>
+      </c>
+      <c r="D446" t="n">
+        <v>326.9</v>
+      </c>
+      <c r="E446" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="F446" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="G446" t="n">
+        <v>333.22</v>
+      </c>
+      <c r="H446" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="I446" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B468"/>
+  <dimension ref="A1:B469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21161,6 +21197,16 @@
       </c>
       <c r="B468" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -21329,28 +21375,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3056748809444349</v>
+        <v>-0.3081814595731865</v>
       </c>
       <c r="J2" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K2" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.130334366339046</v>
+        <v>0.1324811044435514</v>
       </c>
       <c r="M2" t="n">
-        <v>4.85118111338569</v>
+        <v>4.853753297033454</v>
       </c>
       <c r="N2" t="n">
-        <v>37.66654199887364</v>
+        <v>37.66359680239275</v>
       </c>
       <c r="O2" t="n">
-        <v>6.137307389961305</v>
+        <v>6.137067443200601</v>
       </c>
       <c r="P2" t="n">
-        <v>340.1297426795393</v>
+        <v>340.1559643651504</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21407,28 +21453,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3663394211977466</v>
+        <v>-0.3676770880805925</v>
       </c>
       <c r="J3" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K3" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2040290242235062</v>
+        <v>0.2058537953462222</v>
       </c>
       <c r="M3" t="n">
-        <v>4.571321963455968</v>
+        <v>4.568083134364806</v>
       </c>
       <c r="N3" t="n">
-        <v>31.63118581754031</v>
+        <v>31.58337193708146</v>
       </c>
       <c r="O3" t="n">
-        <v>5.624160898973313</v>
+        <v>5.619908534583232</v>
       </c>
       <c r="P3" t="n">
-        <v>338.6483476907003</v>
+        <v>338.6623412195895</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21485,28 +21531,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2388080055570191</v>
+        <v>-0.2398723955395736</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K4" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L4" t="n">
-        <v>0.163150015885964</v>
+        <v>0.1648921872589942</v>
       </c>
       <c r="M4" t="n">
-        <v>3.367444506351017</v>
+        <v>3.364595820239792</v>
       </c>
       <c r="N4" t="n">
-        <v>17.67262813185996</v>
+        <v>17.64764610379766</v>
       </c>
       <c r="O4" t="n">
-        <v>4.203882506904772</v>
+        <v>4.200910151835869</v>
       </c>
       <c r="P4" t="n">
-        <v>335.9273210212963</v>
+        <v>335.938455760566</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21563,28 +21609,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05091203855506196</v>
+        <v>-0.05216920907500726</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01547001683335369</v>
+        <v>0.01627217434050121</v>
       </c>
       <c r="M5" t="n">
-        <v>2.484562460312208</v>
+        <v>2.485652059446382</v>
       </c>
       <c r="N5" t="n">
-        <v>9.966026059585223</v>
+        <v>9.96418187373693</v>
       </c>
       <c r="O5" t="n">
-        <v>3.156901338272266</v>
+        <v>3.156609236781919</v>
       </c>
       <c r="P5" t="n">
-        <v>335.2675778806471</v>
+        <v>335.2807293253117</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21641,28 +21687,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01813493454810108</v>
+        <v>0.01682677478663422</v>
       </c>
       <c r="J6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001608736212026729</v>
+        <v>0.001389259004004439</v>
       </c>
       <c r="M6" t="n">
-        <v>2.849863523021642</v>
+        <v>2.849314469556737</v>
       </c>
       <c r="N6" t="n">
-        <v>12.33078721873343</v>
+        <v>12.32532984577159</v>
       </c>
       <c r="O6" t="n">
-        <v>3.511522065818957</v>
+        <v>3.510744913230182</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3762714933046</v>
+        <v>337.3899563438817</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21719,28 +21765,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1057743405776874</v>
+        <v>-0.1075151854067815</v>
       </c>
       <c r="J7" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K7" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0342312853234833</v>
+        <v>0.03541513356295478</v>
       </c>
       <c r="M7" t="n">
-        <v>3.650851851176482</v>
+        <v>3.650938884858449</v>
       </c>
       <c r="N7" t="n">
-        <v>19.07012165070148</v>
+        <v>19.06667438368665</v>
       </c>
       <c r="O7" t="n">
-        <v>4.36693504081541</v>
+        <v>4.366540322003984</v>
       </c>
       <c r="P7" t="n">
-        <v>340.2857676988257</v>
+        <v>340.3039789311734</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21797,28 +21843,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2078344771059488</v>
+        <v>-0.2088627919194994</v>
       </c>
       <c r="J8" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K8" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1147255762690159</v>
+        <v>0.1161380565488448</v>
       </c>
       <c r="M8" t="n">
-        <v>3.705215100122515</v>
+        <v>3.702435240900028</v>
       </c>
       <c r="N8" t="n">
-        <v>20.1370449708586</v>
+        <v>20.10554324973746</v>
       </c>
       <c r="O8" t="n">
-        <v>4.487431890386594</v>
+        <v>4.483920522236925</v>
       </c>
       <c r="P8" t="n">
-        <v>345.8999093931506</v>
+        <v>345.9106667448015</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21875,28 +21921,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1277792468717529</v>
+        <v>-0.1286505236267759</v>
       </c>
       <c r="J9" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K9" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205499154309083</v>
+        <v>0.1223492202908982</v>
       </c>
       <c r="M9" t="n">
-        <v>2.104615050888059</v>
+        <v>2.105113610763823</v>
       </c>
       <c r="N9" t="n">
-        <v>7.196276095445568</v>
+        <v>7.189975772143874</v>
       </c>
       <c r="O9" t="n">
-        <v>2.682587574608808</v>
+        <v>2.681413017821737</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6711908435022</v>
+        <v>356.6803053970568</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21934,7 +21980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J445"/>
+  <dimension ref="A1:J446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45077,6 +45123,58 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-42.52598269520075,173.50250955845166</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-42.52664095299502,173.50241361628267</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-42.52730070601949,173.50233815017418</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-42.527963620874935,173.5022936872</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-42.52863002712452,173.50225822143724</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-42.52929487337198,173.5022129379595</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-42.52996099056498,173.50224169466017</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-42.53061896848054,173.5024462142234</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0397/nzd0397.xlsx
+++ b/data/nzd0397/nzd0397.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J446"/>
+  <dimension ref="A1:J447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16500,6 +16500,42 @@
       <c r="J446" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="C447" t="n">
+        <v>327.58</v>
+      </c>
+      <c r="D447" t="n">
+        <v>328.16</v>
+      </c>
+      <c r="E447" t="n">
+        <v>332.26</v>
+      </c>
+      <c r="F447" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="G447" t="n">
+        <v>333.08</v>
+      </c>
+      <c r="H447" t="n">
+        <v>337.93</v>
+      </c>
+      <c r="I447" t="n">
+        <v>351.2</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16514,7 +16550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B469"/>
+  <dimension ref="A1:B470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21207,6 +21243,16 @@
       </c>
       <c r="B469" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -21375,28 +21421,28 @@
         <v>0.113</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3081814595731865</v>
+        <v>-0.3094842848394361</v>
       </c>
       <c r="J2" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1324811044435514</v>
+        <v>0.1339300713227258</v>
       </c>
       <c r="M2" t="n">
-        <v>4.853753297033454</v>
+        <v>4.849793532609946</v>
       </c>
       <c r="N2" t="n">
-        <v>37.66359680239275</v>
+        <v>37.60104605624748</v>
       </c>
       <c r="O2" t="n">
-        <v>6.137067443200601</v>
+        <v>6.131969182591142</v>
       </c>
       <c r="P2" t="n">
-        <v>340.1559643651504</v>
+        <v>340.1696620576118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21453,28 +21499,28 @@
         <v>0.0924</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3676770880805925</v>
+        <v>-0.3681341107576628</v>
       </c>
       <c r="J3" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K3" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2058537953462222</v>
+        <v>0.2070158933114853</v>
       </c>
       <c r="M3" t="n">
-        <v>4.568083134364806</v>
+        <v>4.560213824025456</v>
       </c>
       <c r="N3" t="n">
-        <v>31.58337193708146</v>
+        <v>31.51525173423483</v>
       </c>
       <c r="O3" t="n">
-        <v>5.619908534583232</v>
+        <v>5.61384464820989</v>
       </c>
       <c r="P3" t="n">
-        <v>338.6623412195895</v>
+        <v>338.6671462815119</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21531,28 +21577,28 @@
         <v>0.0993</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2398723955395736</v>
+        <v>-0.2403970032736444</v>
       </c>
       <c r="J4" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K4" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1648921872589942</v>
+        <v>0.1661162048918871</v>
       </c>
       <c r="M4" t="n">
-        <v>3.364595820239792</v>
+        <v>3.359345933482935</v>
       </c>
       <c r="N4" t="n">
-        <v>17.64764610379766</v>
+        <v>17.61162779063698</v>
       </c>
       <c r="O4" t="n">
-        <v>4.200910151835869</v>
+        <v>4.196620996782647</v>
       </c>
       <c r="P4" t="n">
-        <v>335.938455760566</v>
+        <v>335.9439714007599</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21609,28 +21655,28 @@
         <v>0.1181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05216920907500726</v>
+        <v>-0.05283590693116243</v>
       </c>
       <c r="J5" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K5" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01627217434050121</v>
+        <v>0.01675144604624379</v>
       </c>
       <c r="M5" t="n">
-        <v>2.485652059446382</v>
+        <v>2.48357436694999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.96418187373693</v>
+        <v>9.947574768953684</v>
       </c>
       <c r="O5" t="n">
-        <v>3.156609236781919</v>
+        <v>3.153977610724858</v>
       </c>
       <c r="P5" t="n">
-        <v>335.2807293253117</v>
+        <v>335.2877388778855</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21687,28 +21733,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01682677478663422</v>
+        <v>0.01555297410745479</v>
       </c>
       <c r="J6" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K6" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001389259004004439</v>
+        <v>0.001190680000927813</v>
       </c>
       <c r="M6" t="n">
-        <v>2.849314469556737</v>
+        <v>2.848549125095201</v>
       </c>
       <c r="N6" t="n">
-        <v>12.32532984577159</v>
+        <v>12.31862658393018</v>
       </c>
       <c r="O6" t="n">
-        <v>3.510744913230182</v>
+        <v>3.509790105395219</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3899563438817</v>
+        <v>337.4033488765664</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21765,28 +21811,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1075151854067815</v>
+        <v>-0.1093032621457647</v>
       </c>
       <c r="J7" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K7" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03541513356295478</v>
+        <v>0.03664866326818972</v>
       </c>
       <c r="M7" t="n">
-        <v>3.650938884858449</v>
+        <v>3.651159987102055</v>
       </c>
       <c r="N7" t="n">
-        <v>19.06667438368665</v>
+        <v>19.0651698394031</v>
       </c>
       <c r="O7" t="n">
-        <v>4.366540322003984</v>
+        <v>4.366368037557427</v>
       </c>
       <c r="P7" t="n">
-        <v>340.3039789311734</v>
+        <v>340.322778478513</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21843,28 +21889,28 @@
         <v>0.1026</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2088627919194994</v>
+        <v>-0.2098205497349561</v>
       </c>
       <c r="J8" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K8" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1161380565488448</v>
+        <v>0.1175056528363888</v>
       </c>
       <c r="M8" t="n">
-        <v>3.702435240900028</v>
+        <v>3.699238800856947</v>
       </c>
       <c r="N8" t="n">
-        <v>20.10554324973746</v>
+        <v>20.07229722284896</v>
       </c>
       <c r="O8" t="n">
-        <v>4.483920522236925</v>
+        <v>4.480211738617825</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9106667448015</v>
+        <v>345.9207364543385</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21921,28 +21967,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1286505236267759</v>
+        <v>-0.1294745729906356</v>
       </c>
       <c r="J9" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K9" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1223492202908982</v>
+        <v>0.1241042548866224</v>
       </c>
       <c r="M9" t="n">
-        <v>2.105113610763823</v>
+        <v>2.105282013726588</v>
       </c>
       <c r="N9" t="n">
-        <v>7.189975772143874</v>
+        <v>7.18261495733072</v>
       </c>
       <c r="O9" t="n">
-        <v>2.681413017821737</v>
+        <v>2.680040103679555</v>
       </c>
       <c r="P9" t="n">
-        <v>356.6803053970568</v>
+        <v>356.6889693177311</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21980,7 +22026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J446"/>
+  <dimension ref="A1:J447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45175,6 +45221,58 @@
         </is>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-42.5259852195291,173.50254396733544</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-42.526642792924434,173.5024386962587</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-42.527301825982384,173.5023534164064</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-42.52796479045614,173.50231065958866</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-42.528630062674985,173.50225907238448</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-42.5292948406906,173.502211233907</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-42.52996097568675,173.5022432774155</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-42.53061892686248,173.50244730863145</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
